--- a/report_template.xlsx
+++ b/report_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seonghona/Documents/Lectures/Customer/LearningClue/SSE_DS/data_dummy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seonghona/Documents/Lectures/Customer/LearningClue/SSE_DS/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEC7096-58D4-334E-98F3-1772F33B441D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BAA31B-B655-5B4F-9A93-434A85DE2042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22380" yWindow="3760" windowWidth="24420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54500" yWindow="2620" windowWidth="24420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="품질_보고서" sheetId="1" r:id="rId1"/>
@@ -325,7 +325,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -635,13 +635,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -656,6 +656,43 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -665,46 +702,18 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -885,12 +894,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="40" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -911,24 +920,24 @@
       <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="10"/>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -963,36 +972,36 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="20" customHeight="1">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
     </row>
     <row r="12" spans="1:4" ht="20" customHeight="1">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1">
       <c r="A16" s="14" t="s">
@@ -1003,24 +1012,20 @@
       <c r="D16" s="16"/>
     </row>
     <row r="17" spans="1:4" ht="60" customHeight="1">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
     </row>
     <row r="19" spans="1:4" ht="16" customHeight="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="13" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:D16"/>
+  <mergeCells count="1">
     <mergeCell ref="A17:D17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
